--- a/SeaAroundUsExtraction/global_output/regional_calculations/LME_064_Central_Arctic_Ocean.xlsx
+++ b/SeaAroundUsExtraction/global_output/regional_calculations/LME_064_Central_Arctic_Ocean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R388f7a627907453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R77fb5333dc95401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R72bc91d048224057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R02a04ef19e464c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf8cb4f41f02a4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd8107a436f584dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re0f3ec029dff42a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R55d77a8ea7394795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R277134b7fca34c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd14664a3334f403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9f671f7a4e224fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R917f596b479d49a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="0.0"/>
+    <x:numFmt numFmtId="200" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -78,8 +78,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="22">
-    <x:border/>
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -170,101 +169,6 @@
       <x:top style="thin">
         <x:color rgb="FFD0D5DD"/>
       </x:top>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:bottom style="medium">
-        <x:color rgb="FF147D92"/>
-      </x:bottom>
     </x:border>
     <x:border>
       <x:bottom style="medium">
@@ -275,37 +179,32 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -321,60 +220,30 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -384,9 +253,26 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LME064ValidationTable" displayName="LME064ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LME064ValidationTable" displayName="LME064ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -616,67 +502,67 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
@@ -690,67 +576,27 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -763,67 +609,27 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -859,67 +665,67 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
@@ -939,273 +745,245 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>check</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>unit</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
         <x:v>raw_filtered_tonnes</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="n">
+      <x:c r="C2" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D2" s="46" t="str">
+      <x:c r="D2" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
         <x:v>species_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C3" s="46" t="n">
+      <x:c r="C3" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D3" s="46" t="str">
+      <x:c r="D3" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
         <x:v>catch_difference_tonnes</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="n">
+      <x:c r="C4" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="46" t="str">
+      <x:c r="D4" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D5" s="46" t="str">
+      <x:c r="C5" s="30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>matched_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="n">
+      <x:c r="C6" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="46" t="str">
+      <x:c r="D6" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
-      <x:c r="A7" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="A7" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="str">
         <x:v>catch_coverage_fraction</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="str"/>
-      <x:c r="D7" s="46" t="str">
+      <x:c r="C7" s="24" t="str"/>
+      <x:c r="D7" s="24" t="str">
         <x:v>fraction</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
-      <x:c r="A8" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="A8" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
         <x:v>taxa_count</x:v>
       </x:c>
-      <x:c r="C8" s="46" t="n">
+      <x:c r="C8" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D8" s="46" t="str">
+      <x:c r="D8" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
-      <x:c r="A9" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="A9" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
         <x:v>matched_taxa_count</x:v>
       </x:c>
-      <x:c r="C9" s="46" t="n">
+      <x:c r="C9" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D9" s="46" t="str">
+      <x:c r="D9" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="A10" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
         <x:v>unmatched_taxa_count</x:v>
       </x:c>
-      <x:c r="C10" s="46" t="n">
+      <x:c r="C10" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="46" t="str">
+      <x:c r="D10" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
-      <x:c r="A11" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="A11" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="str">
         <x:v>species_ppr</x:v>
       </x:c>
-      <x:c r="C11" s="46" t="n">
+      <x:c r="C11" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="46" t="str">
+      <x:c r="D11" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
-      <x:c r="A12" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="A12" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
         <x:v>commercial_ppr</x:v>
       </x:c>
-      <x:c r="C12" s="46" t="n">
+      <x:c r="C12" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="46" t="str">
+      <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
-      <x:c r="A13" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="A13" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B13" s="24" t="str">
         <x:v>functional_ppr</x:v>
       </x:c>
-      <x:c r="C13" s="46" t="n">
+      <x:c r="C13" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="46" t="str">
+      <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
-      <x:c r="A14" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="A14" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B14" s="24" t="str">
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
-      <x:c r="C14" s="46" t="n">
+      <x:c r="C14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="46" t="str">
+      <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
-      <x:c r="A15" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="A15" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B15" s="24" t="str">
         <x:v>functional_ppr_difference</x:v>
       </x:c>
-      <x:c r="C15" s="46" t="n">
+      <x:c r="C15" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="46" t="str">
+      <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
-      <x:c r="A16" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B16" s="46" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D16" s="46" t="str">
+      <x:c r="A16" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
-      <x:c r="A17" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B17" s="46" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D17" s="46" t="str">
+      <x:c r="A17" s="24" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="B17" s="24" t="str">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="46" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="46" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="46" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77a2036b4eb411b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2bc5ab5cdbb4ee1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1220,152 +998,152 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="3" t="str">
         <x:v>LME_064 - Central Arctic Ocean</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>Notes / source</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="42" t="str">
+      <x:c r="A4" s="22" t="str">
         <x:v>Unit ID</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="str">
-        <x:v>LME_064</x:v>
-      </x:c>
-      <x:c r="C4" s="32" t="str">
+      <x:c r="B4" s="17" t="str">
+        <x:v>LME_064</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
         <x:v>Sea Around Us region identifier</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="42" t="str">
+      <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="58" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C5" s="32" t="str">
+      <x:c r="C5" s="18" t="str">
         <x:v>Used by every SPPR formula</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42" t="str">
+      <x:c r="A6" s="22" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="18" t="str">
         <x:v>Latest year common to all 84 datasets</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="42" t="str">
+      <x:c r="A7" s="22" t="str">
         <x:v>Region type</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
+      <x:c r="B7" s="17" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C7" s="18" t="str">
         <x:v>Sea Around Us spatial classification</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="42" t="str">
+      <x:c r="A8" s="22" t="str">
         <x:v>Catch scope</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>Landings + Discards</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
+      <x:c r="C8" s="18" t="str">
         <x:v>Reported + unreported; all sectors, gears, entities, and end uses</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42" t="str">
+      <x:c r="A9" s="22" t="str">
         <x:v>SPPR formula</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="17" t="str">
         <x:v>(1 / TE)^(TL - 1)</x:v>
       </x:c>
-      <x:c r="C9" s="32" t="str">
+      <x:c r="C9" s="18" t="str">
         <x:v>TE is the Metadata!B5 value</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42" t="str">
+      <x:c r="A10" s="22" t="str">
         <x:v>PPR formula</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>Catch tonnes × SPPR</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
+      <x:c r="C10" s="18" t="str">
         <x:v>Unit: tonnes primary-production equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42" t="str">
+      <x:c r="A11" s="22" t="str">
         <x:v>Wet-weight/carbon divisor</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="str">
+      <x:c r="B11" s="17" t="str">
         <x:v>Not applied</x:v>
       </x:c>
-      <x:c r="C11" s="32" t="str">
+      <x:c r="C11" s="18" t="str">
         <x:v>The paper's /9 conversion is intentionally omitted</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42" t="str">
+      <x:c r="A12" s="22" t="str">
         <x:v>Primary TL source</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="C12" s="32" t="str">
+      <x:c r="C12" s="18" t="str">
         <x:v>No SPPR regression from the supplement is used</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="42" t="str">
+      <x:c r="A13" s="22" t="str">
         <x:v>Secondary TL source</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="str">
+      <x:c r="B13" s="17" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="C13" s="32" t="str">
+      <x:c r="C13" s="18" t="str">
         <x:v>Exact taxon matches, followed by documented fallbacks</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="42" t="str">
+      <x:c r="A14" s="22" t="str">
         <x:v>Catch data URL</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:v>https://www.seaaroundus.org/data/</x:v>
       </x:c>
-      <x:c r="C14" s="32" t="str">
+      <x:c r="C14" s="18" t="str">
         <x:v>Frozen archive: raw_data/SAU_downloads/LME_064-catch.zip</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="43" t="str">
+      <x:c r="A15" s="23" t="str">
         <x:v>Method source</x:v>
       </x:c>
-      <x:c r="B15" s="34" t="str">
+      <x:c r="B15" s="20" t="str">
         <x:v>Pauly &amp; Christensen (1995)</x:v>
       </x:c>
-      <x:c r="C15" s="35" t="str">
+      <x:c r="C15" s="21" t="str">
         <x:v>Nature 374:255-257</x:v>
       </x:c>
     </x:row>
